--- a/plantillas/prueba_importacion.xlsx
+++ b/plantillas/prueba_importacion.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Procesos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,574 +425,489 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fecha de Inicio</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Fecha de Inicio</t>
+          <t>CLIENTE</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>CLIENTE</t>
+          <t>Sub Cliente</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Sub Cliente</t>
+          <t>Tipo Proceso</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Tipo Proceso</t>
+          <t>Ciudad</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Ciudad</t>
+          <t>Cédula</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Cédula</t>
+          <t>Nombre Completo</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Nombre Completo</t>
+          <t>Cargo</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Cargo</t>
+          <t>Fecha Fin</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Fecha Fin</t>
+          <t>Estatus</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Estatus</t>
+          <t>No Factura</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>No Factura</t>
+          <t>Orden Compra</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Orden Compra</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>4</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>VEHICULOS PARKER</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VEHICULOS PARKER</t>
+          <t>CARRETAS TIO VIVO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CARRETAS TIO VIVO</t>
+          <t>POL. PREEMPLEO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>POL. PREEMPLEO</t>
+          <t>MEDELLIN</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MEDELLIN</t>
+          <t>1098223344</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1098223344</t>
+          <t>LUCIA FERNANDEZ</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>LUCIA FERNANDEZ</t>
+          <t>CONDUCTORA</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CONDUCTORA</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>terminado</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>terminado</t>
+          <t>FA-2001</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>FA-2001</t>
+          <t>OC-7001</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>OC-7001</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>fecha dd/mm/aaaa y estado sinonimo</t>
+          <t>valida: fecha dd/mm/aaaa y sinonimo de estado</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>5</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>ADISPETROL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ADISPETROL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ESTUDIO DE SEGURIDAD</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ESTUDIO DE SEGURIDAD</t>
+          <t>BARRANQUILLA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BARRANQUILLA</t>
+          <t>1055667788</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1055667788</t>
+          <t>JORGE MENDEZ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>JORGE MENDEZ</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
           <t>SUPERVISOR</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>en trámite</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>OC-7002</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>OC-7002</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>estado con tilde, sin fecha fin</t>
+          <t>valida: estado con tilde, sin fecha fin</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>6</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>TORRES DELUXE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TORRES DELUXE</t>
+          <t>APTO. 512</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>APTO. 512</t>
+          <t>POL. PREEMPLEO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>POL. PREEMPLEO</t>
+          <t>BOGOTA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BOGOTA</t>
+          <t>877665544</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>877665544</t>
+          <t>ANA MARIA RUIZ</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ANA MARIA RUIZ</t>
+          <t>ADMINISTRADORA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ADMINISTRADORA</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>FINALIZADO</t>
+          <t>FA-1990</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>FA-1990</t>
+          <t>OC-6905</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>OC-6905</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>fecha en formato aaaa-mm-dd</t>
+          <t>valida: fecha aaaa-mm-dd</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>7</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>CONSTRUCTORA DEL CARIBE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CONSTRUCTORA DEL CARIBE</t>
+          <t>OBRA CENTRO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OBRA CENTRO</t>
+          <t>VISITA DOMICILIARIA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VISITA DOMICILIARIA</t>
+          <t>CARTAGENA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CARTAGENA</t>
+          <t>1144778899</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1144778899</t>
+          <t>DIEGO CASTANO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DIEGO CASTANO</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
           <t>OFICIAL DE OBRA</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>OC-6906</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>OC-6906</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>estado vacio: queda PENDIENTE</t>
+          <t>valida: estado vacio queda PENDIENTE</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>8</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>ADISPETROL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ADISPETROL</t>
+          <t>PLANTA NORTE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PLANTA NORTE</t>
+          <t>POLIGRAFIA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>POLIGRAFIA</t>
+          <t>SANTA MARTA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SANTA MARTA</t>
+          <t>1033445566</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1033445566</t>
+          <t>PAOLA GUERRERO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>PAOLA GUERRERO</t>
+          <t>ANALISTA</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ANALISTA</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>cancelado</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>FA-1880</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>FA-1880</t>
+          <t>OC-6801</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>OC-6801</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>sinonimo de ANULADO</t>
+          <t>valida: sinonimo de ANULADO</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>VEHICULOS PARKER</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CARRETAS TIO VIVO</t>
+          <t>POL. PREEMPLEO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>POL. PREEMPLEO</t>
+          <t>CALI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MEDELLIN</t>
+          <t>1099887766</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1037846532</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>MARIO SANTODOMINGO</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>CONDUCTOR</t>
-        </is>
-      </c>
+          <t>SIN CLIENTE</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>DUPLICADO: ya existe en la base, debe omitirse</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ERROR: falta el cliente</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>10</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>31/02/2026</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>ADISPETROL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>POLIGRAFIA</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>POL. PREEMPLEO</t>
+          <t>CALI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CALI</t>
+          <t>1088776655</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1099887766</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>SIN CLIENTE</t>
-        </is>
-      </c>
+          <t>FECHA MALA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>ERROR: falta el cliente</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ERROR: 31 de febrero no existe</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>11</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>31/02/2026</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ADISPETROL</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>POLIGRAFIA</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>CALI</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>1088776655</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>FECHA MALA</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>ERROR: 31 de febrero no existe</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+    <row r="9"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
